--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0003T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0003T0006Z000C1N25_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>75.66831863101255</v>
       </c>
       <c r="E2" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F2" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>71.37855488263224</v>
       </c>
       <c r="E3" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F3" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>71.49463932877302</v>
       </c>
       <c r="E4" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F4" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>44.04781510334763</v>
       </c>
       <c r="E5" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F5" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -614,10 +614,10 @@
         <v>66.34388525788275</v>
       </c>
       <c r="E6" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F6" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>43.16537964619332</v>
       </c>
       <c r="E7" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F7" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -678,10 +678,10 @@
         <v>37.10795063055895</v>
       </c>
       <c r="E8" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F8" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         <v>50.99516743118302</v>
       </c>
       <c r="E9" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F9" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,10 +742,10 @@
         <v>47.18180653293518</v>
       </c>
       <c r="E10" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F10" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -774,10 +774,10 @@
         <v>54.60225905626852</v>
       </c>
       <c r="E11" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F11" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
         <v>57.48067308041702</v>
       </c>
       <c r="E12" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F12" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -838,10 +838,10 @@
         <v>50.40028882665441</v>
       </c>
       <c r="E13" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F13" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>39.15527264592296</v>
       </c>
       <c r="E14" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F14" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
         <v>51.65486829994082</v>
       </c>
       <c r="E15" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F15" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
         <v>59.36325085390756</v>
       </c>
       <c r="E16" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F16" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
         <v>44.10807103308859</v>
       </c>
       <c r="E17" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F17" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -998,10 +998,10 @@
         <v>27.70341739035599</v>
       </c>
       <c r="E18" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F18" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1030,10 +1030,10 @@
         <v>29.96692374318257</v>
       </c>
       <c r="E19" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F19" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1062,10 +1062,10 @@
         <v>32.5224489699449</v>
       </c>
       <c r="E20" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F20" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1094,10 +1094,10 @@
         <v>18.58090417606205</v>
       </c>
       <c r="E21" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F21" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1126,10 +1126,10 @@
         <v>30.4414438471806</v>
       </c>
       <c r="E22" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F22" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1158,10 +1158,10 @@
         <v>44.4221668835235</v>
       </c>
       <c r="E23" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F23" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
         <v>40.77376062609098</v>
       </c>
       <c r="E24" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F24" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1222,10 +1222,10 @@
         <v>18.40107356505786</v>
       </c>
       <c r="E25" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F25" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
         <v>20.5</v>
       </c>
       <c r="E26" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F26" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1286,10 +1286,10 @@
         <v>30.81054122284341</v>
       </c>
       <c r="E27" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F27" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1318,10 +1318,10 @@
         <v>23.70359799083187</v>
       </c>
       <c r="E28" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F28" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         <v>3.558580777192327</v>
       </c>
       <c r="E29" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F29" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1382,10 +1382,10 @@
         <v>9.44464797050728</v>
       </c>
       <c r="E30" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F30" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         <v>19.60229578391266</v>
       </c>
       <c r="E31" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F31" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1446,10 +1446,10 @@
         <v>28.46463957719298</v>
       </c>
       <c r="E32" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F32" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1478,10 +1478,10 @@
         <v>20.29471705666107</v>
       </c>
       <c r="E33" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F33" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         <v>25.63201123595259</v>
       </c>
       <c r="E34" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F34" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1542,10 +1542,10 @@
         <v>24.85881108393594</v>
       </c>
       <c r="E35" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F35" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
         <v>35.27992065247273</v>
       </c>
       <c r="E36" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F36" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1606,10 +1606,10 @@
         <v>26.46591098837226</v>
       </c>
       <c r="E37" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F37" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1638,10 +1638,10 @@
         <v>16.60926575158278</v>
       </c>
       <c r="E38" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F38" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>18.84515573994077</v>
+        <v>48.92085647895466</v>
       </c>
       <c r="D39" t="n">
-        <v>22.13304594147698</v>
+        <v>7.902703700796074</v>
       </c>
       <c r="E39" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F39" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>47.62515476850366</v>
+        <v>18.84515573994077</v>
       </c>
       <c r="D40" t="n">
-        <v>31.44316591656462</v>
+        <v>22.13304594147698</v>
       </c>
       <c r="E40" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F40" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>60.73331939672281</v>
+        <v>47.62515476850366</v>
       </c>
       <c r="D41" t="n">
-        <v>39.71364562470586</v>
+        <v>31.44316591656462</v>
       </c>
       <c r="E41" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F41" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>64.03085786910538</v>
+        <v>60.73331939672281</v>
       </c>
       <c r="D42" t="n">
-        <v>18.69467745144204</v>
+        <v>39.71364562470586</v>
       </c>
       <c r="E42" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F42" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>39.375901040006</v>
+        <v>64.03085786910538</v>
       </c>
       <c r="D43" t="n">
-        <v>31.90643525199998</v>
+        <v>18.69467745144204</v>
       </c>
       <c r="E43" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F43" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>24.7407616426339</v>
+        <v>39.375901040006</v>
       </c>
       <c r="D44" t="n">
-        <v>25.62577353681901</v>
+        <v>31.90643525199998</v>
       </c>
       <c r="E44" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F44" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>26.66346528052763</v>
+        <v>24.7407616426339</v>
       </c>
       <c r="D45" t="n">
-        <v>28.60720227423998</v>
+        <v>25.62577353681901</v>
       </c>
       <c r="E45" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F45" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>38.32253261904076</v>
+        <v>26.66346528052763</v>
       </c>
       <c r="D46" t="n">
-        <v>27.17064505990171</v>
+        <v>28.60720227423998</v>
       </c>
       <c r="E46" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F46" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>62.75488243806382</v>
+        <v>38.32253261904076</v>
       </c>
       <c r="D47" t="n">
-        <v>35.18403555223978</v>
+        <v>27.17064505990171</v>
       </c>
       <c r="E47" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F47" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>49.14420637100416</v>
+        <v>62.75488243806382</v>
       </c>
       <c r="D48" t="n">
-        <v>25.83471421496126</v>
+        <v>35.18403555223978</v>
       </c>
       <c r="E48" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F48" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>53.18062734449742</v>
+        <v>49.14420637100416</v>
       </c>
       <c r="D49" t="n">
-        <v>25.26700353750045</v>
+        <v>25.83471421496126</v>
       </c>
       <c r="E49" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F49" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>18.736330817325</v>
+        <v>53.18062734449742</v>
       </c>
       <c r="D50" t="n">
-        <v>18.1225915935567</v>
+        <v>25.26700353750045</v>
       </c>
       <c r="E50" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F50" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>15.92477565283155</v>
+        <v>18.736330817325</v>
       </c>
       <c r="D51" t="n">
-        <v>16.03382357644753</v>
+        <v>18.1225915935567</v>
       </c>
       <c r="E51" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F51" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>75.24659522195167</v>
+        <v>15.92477565283155</v>
       </c>
       <c r="D52" t="n">
-        <v>50.91570604523763</v>
+        <v>16.03382357644753</v>
       </c>
       <c r="E52" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F52" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>18.29987674413659</v>
+        <v>75.24659522195167</v>
       </c>
       <c r="D53" t="n">
-        <v>13.62208662098101</v>
+        <v>50.91570604523763</v>
       </c>
       <c r="E53" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F53" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>16.91953600984838</v>
+        <v>18.29987674413659</v>
       </c>
       <c r="D54" t="n">
-        <v>15.77872291609606</v>
+        <v>13.62208662098101</v>
       </c>
       <c r="E54" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F54" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>34.73257074760579</v>
+        <v>16.91953600984838</v>
       </c>
       <c r="D55" t="n">
-        <v>7.135022640315685</v>
+        <v>15.77872291609606</v>
       </c>
       <c r="E55" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F55" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>6.880437128328945</v>
+        <v>34.73257074760579</v>
       </c>
       <c r="D56" t="n">
-        <v>7.644970074902967</v>
+        <v>7.135022640315685</v>
       </c>
       <c r="E56" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F56" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>44.31214530496691</v>
+        <v>6.880437128328945</v>
       </c>
       <c r="D57" t="n">
-        <v>11.14051664471227</v>
+        <v>7.644970074902967</v>
       </c>
       <c r="E57" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F57" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>39.11186858920517</v>
+        <v>44.31214530496691</v>
       </c>
       <c r="D58" t="n">
-        <v>13.50102876738576</v>
+        <v>11.14051664471227</v>
       </c>
       <c r="E58" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F58" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>22.61576822309784</v>
+        <v>39.11186858920517</v>
       </c>
       <c r="D59" t="n">
-        <v>15.09166968997206</v>
+        <v>13.50102876738576</v>
       </c>
       <c r="E59" t="n">
-        <v>25.49854683336459</v>
+        <v>25.289723492676</v>
       </c>
       <c r="F59" t="n">
-        <v>17.19598848032586</v>
+        <v>17.32644882990657</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2336,23 +2336,55 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
+        <v>22.61576822309784</v>
+      </c>
+      <c r="D60" t="n">
+        <v>15.09166968997206</v>
+      </c>
+      <c r="E60" t="n">
+        <v>25.289723492676</v>
+      </c>
+      <c r="F60" t="n">
+        <v>17.32644882990657</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>T1791</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>W0051F0003T0006Z000C1N25.png</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>60</v>
+      </c>
+      <c r="C61" t="n">
         <v>7.367217856684783</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D61" t="n">
         <v>8.920851011637415</v>
       </c>
-      <c r="E60" t="n">
-        <v>25.49854683336459</v>
-      </c>
-      <c r="F60" t="n">
-        <v>17.19598848032586</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>T1791</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
+      <c r="E61" t="n">
+        <v>25.289723492676</v>
+      </c>
+      <c r="F61" t="n">
+        <v>17.32644882990657</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>T1791</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0003T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0003T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>113.4294195336963</v>
+        <v>18.43228067422565</v>
       </c>
       <c r="D2" t="n">
-        <v>75.66831863101255</v>
+        <v>12.29610177753954</v>
       </c>
       <c r="E2" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F2" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>76.84920886328561</v>
+        <v>12.48799644028391</v>
       </c>
       <c r="D3" t="n">
-        <v>71.37855488263224</v>
+        <v>11.59901516842774</v>
       </c>
       <c r="E3" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F3" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>74.26095270916178</v>
+        <v>12.06740481523879</v>
       </c>
       <c r="D4" t="n">
-        <v>71.49463932877302</v>
+        <v>11.61787889092562</v>
       </c>
       <c r="E4" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F4" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>68.19255751903464</v>
+        <v>11.08129059684313</v>
       </c>
       <c r="D5" t="n">
-        <v>44.04781510334763</v>
+        <v>7.157769954293991</v>
       </c>
       <c r="E5" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F5" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>106.3232152731757</v>
+        <v>17.27752248189105</v>
       </c>
       <c r="D6" t="n">
-        <v>66.34388525788275</v>
+        <v>10.78088135440595</v>
       </c>
       <c r="E6" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F6" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>62.59473070734276</v>
+        <v>10.1716437399432</v>
       </c>
       <c r="D7" t="n">
-        <v>43.16537964619332</v>
+        <v>7.014374192506414</v>
       </c>
       <c r="E7" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F7" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>70.4741140219666</v>
+        <v>11.45204352856957</v>
       </c>
       <c r="D8" t="n">
-        <v>37.10795063055895</v>
+        <v>6.030041977465829</v>
       </c>
       <c r="E8" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F8" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>91.043247340779</v>
+        <v>14.79452769287659</v>
       </c>
       <c r="D9" t="n">
-        <v>50.99516743118302</v>
+        <v>8.28671470756724</v>
       </c>
       <c r="E9" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F9" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>57.69168982111588</v>
+        <v>9.37489959593133</v>
       </c>
       <c r="D10" t="n">
-        <v>47.18180653293518</v>
+        <v>7.667043561601967</v>
       </c>
       <c r="E10" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F10" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>57.65773233901323</v>
+        <v>9.369381505089651</v>
       </c>
       <c r="D11" t="n">
-        <v>54.60225905626852</v>
+        <v>8.872867096643635</v>
       </c>
       <c r="E11" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F11" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>98.62543551374664</v>
+        <v>16.02663327098383</v>
       </c>
       <c r="D12" t="n">
-        <v>57.48067308041702</v>
+        <v>9.340609375567766</v>
       </c>
       <c r="E12" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F12" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>52.94249872694953</v>
+        <v>8.603156043129299</v>
       </c>
       <c r="D13" t="n">
-        <v>50.40028882665441</v>
+        <v>8.190046934331342</v>
       </c>
       <c r="E13" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F13" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78.29394287374615</v>
+        <v>12.72276571698375</v>
       </c>
       <c r="D14" t="n">
-        <v>39.15527264592296</v>
+        <v>6.362731804962481</v>
       </c>
       <c r="E14" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F14" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>53.41747878532271</v>
+        <v>8.68034030261494</v>
       </c>
       <c r="D15" t="n">
-        <v>51.65486829994082</v>
+        <v>8.393916098740382</v>
       </c>
       <c r="E15" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F15" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>62.74160461812852</v>
+        <v>10.19551075044589</v>
       </c>
       <c r="D16" t="n">
-        <v>59.36325085390756</v>
+        <v>9.646528263759979</v>
       </c>
       <c r="E16" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F16" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>47.1629283029531</v>
+        <v>7.663975849229879</v>
       </c>
       <c r="D17" t="n">
-        <v>44.10807103308859</v>
+        <v>7.167561542876896</v>
       </c>
       <c r="E17" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F17" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>29.63781587595819</v>
+        <v>4.816145079843206</v>
       </c>
       <c r="D18" t="n">
-        <v>27.70341739035599</v>
+        <v>4.501805325932849</v>
       </c>
       <c r="E18" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F18" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31.64121165861925</v>
+        <v>5.141696894525628</v>
       </c>
       <c r="D19" t="n">
-        <v>29.96692374318257</v>
+        <v>4.869625108267169</v>
       </c>
       <c r="E19" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F19" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>35.42480638923455</v>
+        <v>5.756531038250615</v>
       </c>
       <c r="D20" t="n">
-        <v>32.5224489699449</v>
+        <v>5.284897957616046</v>
       </c>
       <c r="E20" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F20" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>31.90355150197313</v>
+        <v>5.184327119070633</v>
       </c>
       <c r="D21" t="n">
-        <v>18.58090417606205</v>
+        <v>3.019396928610083</v>
       </c>
       <c r="E21" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F21" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>33.85874476153688</v>
+        <v>5.502046023749743</v>
       </c>
       <c r="D22" t="n">
-        <v>30.4414438471806</v>
+        <v>4.946734625166847</v>
       </c>
       <c r="E22" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F22" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>84.76189153482821</v>
+        <v>13.77380737440958</v>
       </c>
       <c r="D23" t="n">
-        <v>44.4221668835235</v>
+        <v>7.218602118572568</v>
       </c>
       <c r="E23" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F23" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>44.23673799305551</v>
+        <v>7.188469923871521</v>
       </c>
       <c r="D24" t="n">
-        <v>40.77376062609098</v>
+        <v>6.625736101739785</v>
       </c>
       <c r="E24" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F24" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>18.93829507331446</v>
+        <v>3.0774729494136</v>
       </c>
       <c r="D25" t="n">
-        <v>18.40107356505786</v>
+        <v>2.990174454321903</v>
       </c>
       <c r="E25" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F25" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>21.5786126077194</v>
+        <v>3.506524548754403</v>
       </c>
       <c r="D26" t="n">
-        <v>20.5</v>
+        <v>3.33125</v>
       </c>
       <c r="E26" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F26" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>34.2362983303357</v>
+        <v>5.563398478679551</v>
       </c>
       <c r="D27" t="n">
-        <v>30.81054122284341</v>
+        <v>5.006712948712054</v>
       </c>
       <c r="E27" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F27" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>27.16723175557575</v>
+        <v>4.414675160281059</v>
       </c>
       <c r="D28" t="n">
-        <v>23.70359799083187</v>
+        <v>3.851834673510179</v>
       </c>
       <c r="E28" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F28" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>4.887296074146252</v>
+        <v>0.7941856120487659</v>
       </c>
       <c r="D29" t="n">
-        <v>3.558580777192327</v>
+        <v>0.5782693762937531</v>
       </c>
       <c r="E29" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F29" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>12.85190797137518</v>
+        <v>2.088435045348466</v>
       </c>
       <c r="D30" t="n">
-        <v>9.44464797050728</v>
+        <v>1.534755295207433</v>
       </c>
       <c r="E30" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F30" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>25.83926014921965</v>
+        <v>4.198879774248193</v>
       </c>
       <c r="D31" t="n">
-        <v>19.60229578391266</v>
+        <v>3.185373064885807</v>
       </c>
       <c r="E31" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F31" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>47.00385234001457</v>
+        <v>7.638126005252369</v>
       </c>
       <c r="D32" t="n">
-        <v>28.46463957719298</v>
+        <v>4.62550393129386</v>
       </c>
       <c r="E32" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F32" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>16.97157294999644</v>
+        <v>2.757880604374421</v>
       </c>
       <c r="D33" t="n">
-        <v>20.29471705666107</v>
+        <v>3.297891521707424</v>
       </c>
       <c r="E33" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F33" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>34.67951567582107</v>
+        <v>5.635421297320924</v>
       </c>
       <c r="D34" t="n">
-        <v>25.63201123595259</v>
+        <v>4.165201825842296</v>
       </c>
       <c r="E34" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F34" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>27.42577075531971</v>
+        <v>4.456687747739452</v>
       </c>
       <c r="D35" t="n">
-        <v>24.85881108393594</v>
+        <v>4.03955680113959</v>
       </c>
       <c r="E35" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F35" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>65.60681023907358</v>
+        <v>10.66110666384946</v>
       </c>
       <c r="D36" t="n">
-        <v>35.27992065247273</v>
+        <v>5.732987106026818</v>
       </c>
       <c r="E36" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F36" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>61.31250965197262</v>
+        <v>9.963282818445551</v>
       </c>
       <c r="D37" t="n">
-        <v>26.46591098837226</v>
+        <v>4.300710535610493</v>
       </c>
       <c r="E37" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F37" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>17.8425836058974</v>
+        <v>2.899419835958327</v>
       </c>
       <c r="D38" t="n">
-        <v>16.60926575158278</v>
+        <v>2.699005684632202</v>
       </c>
       <c r="E38" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F38" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>48.92085647895466</v>
+        <v>7.949639177830133</v>
       </c>
       <c r="D39" t="n">
-        <v>7.902703700796074</v>
+        <v>1.284189351379362</v>
       </c>
       <c r="E39" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F39" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>18.84515573994077</v>
+        <v>3.062337807740375</v>
       </c>
       <c r="D40" t="n">
-        <v>22.13304594147698</v>
+        <v>3.596619965490009</v>
       </c>
       <c r="E40" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F40" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>47.62515476850366</v>
+        <v>7.739087649881846</v>
       </c>
       <c r="D41" t="n">
-        <v>31.44316591656462</v>
+        <v>5.10951446144175</v>
       </c>
       <c r="E41" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F41" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>60.73331939672281</v>
+        <v>9.869164401967456</v>
       </c>
       <c r="D42" t="n">
-        <v>39.71364562470586</v>
+        <v>6.453467414014702</v>
       </c>
       <c r="E42" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F42" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>64.03085786910538</v>
+        <v>10.40501440372962</v>
       </c>
       <c r="D43" t="n">
-        <v>18.69467745144204</v>
+        <v>3.037885085859332</v>
       </c>
       <c r="E43" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F43" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>39.375901040006</v>
+        <v>6.398583919000975</v>
       </c>
       <c r="D44" t="n">
-        <v>31.90643525199998</v>
+        <v>5.184795728449997</v>
       </c>
       <c r="E44" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F44" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>24.7407616426339</v>
+        <v>4.020373766928008</v>
       </c>
       <c r="D45" t="n">
-        <v>25.62577353681901</v>
+        <v>4.16418819973309</v>
       </c>
       <c r="E45" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F45" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>26.66346528052763</v>
+        <v>4.33281310808574</v>
       </c>
       <c r="D46" t="n">
-        <v>28.60720227423998</v>
+        <v>4.648670369563996</v>
       </c>
       <c r="E46" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F46" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>38.32253261904076</v>
+        <v>6.227411550594123</v>
       </c>
       <c r="D47" t="n">
-        <v>27.17064505990171</v>
+        <v>4.415229822234028</v>
       </c>
       <c r="E47" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F47" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>62.75488243806382</v>
+        <v>10.19766839618537</v>
       </c>
       <c r="D48" t="n">
-        <v>35.18403555223978</v>
+        <v>5.717405777238965</v>
       </c>
       <c r="E48" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F48" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>49.14420637100416</v>
+        <v>7.985933535288177</v>
       </c>
       <c r="D49" t="n">
-        <v>25.83471421496126</v>
+        <v>4.198141059931205</v>
       </c>
       <c r="E49" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F49" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>53.18062734449742</v>
+        <v>8.64185194348083</v>
       </c>
       <c r="D50" t="n">
-        <v>25.26700353750045</v>
+        <v>4.105888074843824</v>
       </c>
       <c r="E50" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F50" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>18.736330817325</v>
+        <v>3.044653757815313</v>
       </c>
       <c r="D51" t="n">
-        <v>18.1225915935567</v>
+        <v>2.944921133952963</v>
       </c>
       <c r="E51" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F51" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>15.92477565283155</v>
+        <v>2.587776043585127</v>
       </c>
       <c r="D52" t="n">
-        <v>16.03382357644753</v>
+        <v>2.605496331172724</v>
       </c>
       <c r="E52" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F52" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>75.24659522195167</v>
+        <v>12.22757172356715</v>
       </c>
       <c r="D53" t="n">
-        <v>50.91570604523763</v>
+        <v>8.273802232351116</v>
       </c>
       <c r="E53" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F53" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>18.29987674413659</v>
+        <v>2.973729970922196</v>
       </c>
       <c r="D54" t="n">
-        <v>13.62208662098101</v>
+        <v>2.213589075909415</v>
       </c>
       <c r="E54" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F54" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>16.91953600984838</v>
+        <v>2.749424601600362</v>
       </c>
       <c r="D55" t="n">
-        <v>15.77872291609606</v>
+        <v>2.56404247386561</v>
       </c>
       <c r="E55" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F55" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>34.73257074760579</v>
+        <v>5.644042746485941</v>
       </c>
       <c r="D56" t="n">
-        <v>7.135022640315685</v>
+        <v>1.159441179051299</v>
       </c>
       <c r="E56" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F56" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>6.880437128328945</v>
+        <v>1.118071033353454</v>
       </c>
       <c r="D57" t="n">
-        <v>7.644970074902967</v>
+        <v>1.242307637171732</v>
       </c>
       <c r="E57" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F57" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>44.31214530496691</v>
+        <v>7.200723612057123</v>
       </c>
       <c r="D58" t="n">
-        <v>11.14051664471227</v>
+        <v>1.810333954765744</v>
       </c>
       <c r="E58" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F58" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>39.11186858920517</v>
+        <v>6.35567864574584</v>
       </c>
       <c r="D59" t="n">
-        <v>13.50102876738576</v>
+        <v>2.193917174700186</v>
       </c>
       <c r="E59" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F59" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>22.61576822309784</v>
+        <v>3.675062336253399</v>
       </c>
       <c r="D60" t="n">
-        <v>15.09166968997206</v>
+        <v>2.45239632462046</v>
       </c>
       <c r="E60" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F60" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2368,16 +2368,16 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>7.367217856684783</v>
+        <v>1.197172901711277</v>
       </c>
       <c r="D61" t="n">
-        <v>8.920851011637415</v>
+        <v>1.44963828939108</v>
       </c>
       <c r="E61" t="n">
-        <v>25.289723492676</v>
+        <v>4.10958006755985</v>
       </c>
       <c r="F61" t="n">
-        <v>17.32644882990657</v>
+        <v>2.815547934859818</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
